--- a/zh-CN/catalogue/benchmark_dataset.xlsx
+++ b/zh-CN/catalogue/benchmark_dataset.xlsx
@@ -26,7 +26,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="阅读说明" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'参考序列'!$A$1:$H$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'参考序列'!$A$1:$M$19</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'参考序列'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'数据集'!$A$2:$Z$54</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'数据集'!$1:$2</definedName>
@@ -601,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.7109375" customWidth="1" min="1" max="1"/>
@@ -612,6 +612,11 @@
     <col width="35.7109375" customWidth="1" min="6" max="6"/>
     <col width="72.7109375" customWidth="1" min="7" max="7"/>
     <col width="65.7109375" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="36" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="65" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="52" customHeight="1">
@@ -622,22 +627,22 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>参考序列/组装</t>
+          <t>参考基因组 / 组装</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>物种/材料</t>
+          <t>物种 / 材料</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>登录号/版本</t>
+          <t>登录号 / 版本</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>参考来源链接</t>
+          <t>NCBI 记录</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -647,12 +652,37 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>用途/关系</t>
+          <t>样本与参考的关系</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>拟议的 FASTA 下载路径</t>
+          <t>FASTA 下载地址</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>预期字节数</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>发布者 MD5</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>组装发布日期</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>信息核对日期</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>发布者校验和地址</t>
         </is>
       </c>
     </row>
@@ -662,7 +692,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>GRCh38</t>
+          <t>GRCh38.p14</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -672,37 +702,60 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>GCF_000001405.39</t>
+          <t>GCF_000001405.40</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>查看来源</t>
+          <t>https://www.ncbi.nlm.nih.gov/datasets/genome/GCF_000001405.40/</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>直接 gzip FASTA 路径</t>
+          <t>NCBI 组装记录；FASTA 直链另列</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>仅提出同物种参考序列；样本、品系、靶标、contig 是否匹配以及 FASTA 内容均未核实。</t>
+          <t>人类参考基因组；尚未检查与各供体的匹配程度。</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>查看来源</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="78" customHeight="1">
+          <t>https://ftp.ncbi.nlm.nih.gov/genomes/all/GCF/000/001/405/GCF_000001405.40_GRCh38.p14/GCF_000001405.40_GRCh38.p14_genomic.fna.gz</t>
+        </is>
+      </c>
+      <c r="I2" s="6" t="n">
+        <v>972898531</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>c30471567037b2b2389d43c908c653e1</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2022-02-03</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>https://ftp.ncbi.nlm.nih.gov/genomes/all/GCF/000/001/405/GCF_000001405.40_GRCh38.p14/md5checksums.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="95" customHeight="1">
       <c r="A3" s="6" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Sscrofa11.1</t>
+          <t>Sscrofa_HxYL_maternal_Yorkshire_Landrace_v2.0</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -712,27 +765,50 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>GCA_000003025.6</t>
+          <t>GCF_054392235.1</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>查看来源</t>
+          <t>https://www.ncbi.nlm.nih.gov/datasets/genome/GCF_054392235.1/</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>登录页面；确切的 FASTA 获取方式仍需确定</t>
+          <t>NCBI 组装记录；FASTA 直链另列</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>仅提出同物种参考序列；样本、品系、靶标、contig 是否匹配以及 FASTA 内容均未核实。</t>
+          <t>Yorkshire/Landrace 猪参考基因组；所选 FASTQ 样本的品种尚未确定。</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>查看来源</t>
+          <t>https://ftp.ncbi.nlm.nih.gov/genomes/all/GCF/054/392/235/GCF_054392235.1_Sscrofa_HxYL_maternal_Yorkshire_Landrace_v2.0/GCF_054392235.1_Sscrofa_HxYL_maternal_Yorkshire_Landrace_v2.0_genomic.fna.gz</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="n">
+        <v>796779932</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>56b9f3d9c185e35e2410611e424ec6eb</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>https://ftp.ncbi.nlm.nih.gov/genomes/all/GCF/054/392/235/GCF_054392235.1_Sscrofa_HxYL_maternal_Yorkshire_Landrace_v2.0/md5checksums.txt</t>
         </is>
       </c>
     </row>
@@ -742,7 +818,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>GRCm38</t>
+          <t>GRCm39</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -752,27 +828,50 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>GCF_000001635.24</t>
+          <t>GCF_000001635.27</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>查看来源</t>
+          <t>https://www.ncbi.nlm.nih.gov/datasets/genome/GCF_000001635.27/</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>直接 gzip FASTA 路径</t>
+          <t>NCBI 组装记录；FASTA 直链另列</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>为小鼠输入提出同物种基因组参考序列；样本、品系和靶标匹配情况及 FASTA 内容均未核实。对于 Smart-seq2，转录本/补丁等价性及辅助 ERCC 版本也尚未分别核实。</t>
+          <t>C57BL/6J 小鼠参考基因组；仍需确认供体亚品系和转录本靶标。ERCC 外源对照需要单独的参考序列。</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>查看来源</t>
+          <t>https://ftp.ncbi.nlm.nih.gov/genomes/all/GCF/000/001/635/GCF_000001635.27_GRCm39/GCF_000001635.27_GRCm39_genomic.fna.gz</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>834262758</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>c0b0c4c3f54d2b480efe68a18bf7e42b</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>2020-06-24</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>https://ftp.ncbi.nlm.nih.gov/genomes/all/GCF/000/001/635/GCF_000001635.27_GRCm39/md5checksums.txt</t>
         </is>
       </c>
     </row>
@@ -782,12 +881,12 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>ASM584</t>
+          <t>ASM584v2</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <t>Escherichia coli str. K-12 substr. MG1655</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -797,22 +896,45 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>查看来源</t>
+          <t>https://www.ncbi.nlm.nih.gov/datasets/genome/GCF_000005845.2/</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>直接 gzip FASTA 路径</t>
+          <t>NCBI 组装记录；FASTA 直链另列</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>仅提出同物种参考序列；样本、品系、靶标、contig 是否匹配以及 FASTA 内容均未核实。</t>
+          <t>MG1655 样本使用 MG1655 参考基因组；尚未测量读段与参考的匹配程度。</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>查看来源</t>
+          <t>https://ftp.ncbi.nlm.nih.gov/genomes/all/GCF/000/005/845/GCF_000005845.2_ASM584v2/GCF_000005845.2_ASM584v2_genomic.fna.gz</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>1379902</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>c13d459b5caa702ff7e1f26fe44b8ad7</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>2013-09-26</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>https://ftp.ncbi.nlm.nih.gov/genomes/all/GCF/000/005/845/GCF_000005845.2_ASM584v2/md5checksums.txt</t>
         </is>
       </c>
     </row>
@@ -822,12 +944,12 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>ASM19595v2 (H37Rv)</t>
+          <t>ASM19595v2</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Mycobacterium tuberculosis</t>
+          <t>Mycobacterium tuberculosis H37Rv</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -837,22 +959,45 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>查看来源</t>
+          <t>https://www.ncbi.nlm.nih.gov/datasets/genome/GCF_000195955.2/</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>直接 gzip FASTA 路径</t>
+          <t>NCBI 组装记录；FASTA 直链另列</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>仅提出同物种参考序列；样本、品系、靶标、contig 是否匹配以及 FASTA 内容均未核实。</t>
+          <t>H37Rv 参考基因组；尚未检查所选样本与该菌株的匹配程度。</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>查看来源</t>
+          <t>https://ftp.ncbi.nlm.nih.gov/genomes/all/GCF/000/195/955/GCF_000195955.2_ASM19595v2/GCF_000195955.2_ASM19595v2_genomic.fna.gz</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>1277508</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>f93726a0a6e57af2bf1173998fbeb546</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>2013-02-01</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>https://ftp.ncbi.nlm.nih.gov/genomes/all/GCF/000/195/955/GCF_000195955.2_ASM19595v2/md5checksums.txt</t>
         </is>
       </c>
     </row>
@@ -872,27 +1017,50 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>GCA_000226075.1</t>
+          <t>GCF_000226075.1</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>查看来源</t>
+          <t>https://www.ncbi.nlm.nih.gov/datasets/genome/GCF_000226075.1/</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>直接 gzip FASTA 路径</t>
+          <t>NCBI 组装记录；FASTA 直链另列</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>仅提出同物种参考序列；样本、品系、靶标、contig 是否匹配以及 FASTA 内容均未核实。</t>
+          <t>Altus 马铃薯输入使用 DM 1-3 516 R44 参考基因组，两者品种不同。</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>查看来源</t>
+          <t>https://ftp.ncbi.nlm.nih.gov/genomes/all/GCF/000/226/075/GCF_000226075.1_SolTub_3.0/GCF_000226075.1_SolTub_3.0_genomic.fna.gz</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>210303167</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>6ba91aa204b3a87501ff3ed5564183fd</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>2011-09-19</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>https://ftp.ncbi.nlm.nih.gov/genomes/all/GCF/000/226/075/GCF_000226075.1_SolTub_3.0/md5checksums.txt</t>
         </is>
       </c>
     </row>
@@ -907,7 +1075,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Saccharomyces cerevisiae</t>
+          <t>Saccharomyces cerevisiae S288C</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -917,22 +1085,45 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>查看来源</t>
+          <t>https://www.ncbi.nlm.nih.gov/datasets/genome/GCF_000146045.2/</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>直接 gzip FASTA 路径</t>
+          <t>NCBI 组装记录；FASTA 直链另列</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>仅提出同物种参考序列；样本、品系、靶标、contig 是否匹配以及 FASTA 内容均未核实。</t>
+          <t>S288C 酵母参考基因组；尚未检查样本品系是否一致。</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>查看来源</t>
+          <t>https://ftp.ncbi.nlm.nih.gov/genomes/all/GCF/000/146/045/GCF_000146045.2_R64/GCF_000146045.2_R64_genomic.fna.gz</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>3843460</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>88c38b957b721dfc50e6c4df03b6242e</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>2014-12-17</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>https://ftp.ncbi.nlm.nih.gov/genomes/all/GCF/000/146/045/GCF_000146045.2_R64/md5checksums.txt</t>
         </is>
       </c>
     </row>
@@ -942,37 +1133,60 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>ASM1463603v1</t>
+          <t>AGIS1.0</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Oryza sativa</t>
+          <t>Oryza sativa Japonica Group</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>GCA_014636035.1</t>
+          <t>GCF_034140825.1</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>查看来源</t>
+          <t>https://www.ncbi.nlm.nih.gov/datasets/genome/GCF_034140825.1/</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>直接 gzip FASTA 路径</t>
+          <t>NCBI 组装记录；FASTA 直链另列</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>仅提出同物种参考序列；样本、品系、靶标、contig 是否匹配以及 FASTA 内容均未核实。</t>
+          <t>日本晴粳稻参考基因组；尚未确认两组水稻输入的品种。</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>查看来源</t>
+          <t>https://ftp.ncbi.nlm.nih.gov/genomes/all/GCF/034/140/825/GCF_034140825.1_ASM3414082v1/GCF_034140825.1_ASM3414082v1_genomic.fna.gz</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>120268131</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>193a5b81b26b57547b1e4c7be4065b89</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>2023-12-06</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>https://ftp.ncbi.nlm.nih.gov/genomes/all/GCF/034/140/825/GCF_034140825.1_ASM3414082v1/md5checksums.txt</t>
         </is>
       </c>
     </row>
@@ -997,22 +1211,45 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>查看来源</t>
+          <t>https://www.ncbi.nlm.nih.gov/datasets/genome/GCF_000001735.4/</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>直接 gzip FASTA 路径</t>
+          <t>NCBI 组装记录；FASTA 直链另列</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>仅提出同物种参考序列；样本、品系、靶标、contig 是否匹配以及 FASTA 内容均未核实。</t>
+          <t>Columbia 拟南芥参考基因组；尚未检查样本和靶标的匹配程度。</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>查看来源</t>
+          <t>https://ftp.ncbi.nlm.nih.gov/genomes/all/GCF/000/001/735/GCF_000001735.4_TAIR10.1/GCF_000001735.4_TAIR10.1_genomic.fna.gz</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>37482399</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>0fed2d7901bf1488f20e7ef6842cd84c</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>2018-03-15</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>https://ftp.ncbi.nlm.nih.gov/genomes/all/GCF/000/001/735/GCF_000001735.4_TAIR10.1/md5checksums.txt</t>
         </is>
       </c>
     </row>
@@ -1032,27 +1269,50 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>GCA_902167145.1</t>
+          <t>GCF_902167145.1</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>查看来源</t>
+          <t>https://www.ncbi.nlm.nih.gov/datasets/genome/GCF_902167145.1/</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>直接 gzip FASTA 路径</t>
+          <t>NCBI 组装记录；FASTA 直链另列</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>为 SW1611 提出同物种但不同自交系的 B73 参考序列。样本、栽培品种和 contig 是否匹配，以及 FASTA 内容均未核实。</t>
+          <t>SW1611 玉米读段使用 B73 参考基因组，两者自交系不同。</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>查看来源</t>
+          <t>https://ftp.ncbi.nlm.nih.gov/genomes/all/GCF/902/167/145/GCF_902167145.1_Zm-B73-REFERENCE-NAM-5.0/GCF_902167145.1_Zm-B73-REFERENCE-NAM-5.0_genomic.fna.gz</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>650091408</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>3fe51a7a675eb0ac410814a41d50c775</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>2020-03-21</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>https://ftp.ncbi.nlm.nih.gov/genomes/all/GCF/902/167/145/GCF_902167145.1_Zm-B73-REFERENCE-NAM-5.0/md5checksums.txt</t>
         </is>
       </c>
     </row>
@@ -1077,22 +1337,45 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>查看来源</t>
+          <t>https://www.ncbi.nlm.nih.gov/datasets/genome/GCF_042767895.1/</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>直接 gzip FASTA 路径</t>
+          <t>NCBI 组装记录；FASTA 直链另列</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>仅提出同物种参考序列；样本、品系、靶标、contig 是否匹配以及 FASTA 内容均未核实。</t>
+          <t>JL-2024 南美白对虾参考基因组；尚未检查与所选样本的匹配程度。</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>查看来源</t>
+          <t>https://ftp.ncbi.nlm.nih.gov/genomes/all/GCF/042/767/895/GCF_042767895.1_ASM4276789v1/GCF_042767895.1_ASM4276789v1_genomic.fna.gz</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>437570644</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>2a71288f90309178c725a8ba0657451d</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>https://ftp.ncbi.nlm.nih.gov/genomes/all/GCF/042/767/895/GCF_042767895.1_ASM4276789v1/md5checksums.txt</t>
         </is>
       </c>
     </row>
@@ -1112,27 +1395,50 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>GCA_016699485.1</t>
+          <t>GCF_016699485.2</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>查看来源</t>
+          <t>https://www.ncbi.nlm.nih.gov/datasets/genome/GCF_016699485.2/</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>直接 gzip FASTA 路径</t>
+          <t>NCBI 组装记录；FASTA 直链另列</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>仅提出同物种参考序列；样本、品系、靶标、contig 是否匹配以及 FASTA 内容均未核实。</t>
+          <t>肉鸡母系参考基因组；尚未检查与所选蛋鸡样本的匹配程度。</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>查看来源</t>
+          <t>https://ftp.ncbi.nlm.nih.gov/genomes/all/GCF/016/699/485/GCF_016699485.2_bGalGal1.mat.broiler.GRCg7b/GCF_016699485.2_bGalGal1.mat.broiler.GRCg7b_genomic.fna.gz</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>327035795</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>51291297e6b693d8d73207509cbba6aa</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>2021-01-19</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>https://ftp.ncbi.nlm.nih.gov/genomes/all/GCF/016/699/485/GCF_016699485.2_bGalGal1.mat.broiler.GRCg7b/md5checksums.txt</t>
         </is>
       </c>
     </row>
@@ -1157,26 +1463,49 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>查看来源</t>
+          <t>https://www.ncbi.nlm.nih.gov/datasets/genome/GCF_000001215.4/</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>直接 gzip FASTA 路径</t>
+          <t>NCBI 组装记录；FASTA 直链另列</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>仅提出同物种参考序列；样本、品系、靶标、contig 是否匹配以及 FASTA 内容均未核实。</t>
+          <t>果蝇参考基因组；尚未检查与所选样本的匹配程度。</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>查看来源</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="62" customHeight="1">
+          <t>https://ftp.ncbi.nlm.nih.gov/genomes/all/GCF/000/001/215/GCF_000001215.4_Release_6_plus_ISO1_MT/GCF_000001215.4_Release_6_plus_ISO1_MT_genomic.fna.gz</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>44235956</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>869cf40e4f5c7ca27d04ca9ae7baee4f</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>2014-08-01</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>https://ftp.ncbi.nlm.nih.gov/genomes/all/GCF/000/001/215/GCF_000001215.4_Release_6_plus_ISO1_MT/md5checksums.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="95" customHeight="1">
       <c r="A15" s="6" t="n">
         <v>14</v>
       </c>
@@ -1187,7 +1516,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>严重急性呼吸综合征冠状病毒 2 型</t>
+          <t>Severe acute respiratory syndrome coronavirus 2</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -1197,24 +1526,37 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>查看来源</t>
+          <t>https://www.ncbi.nlm.nih.gov/nuccore/NC_045512.2</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>登录页面；确切的 FASTA 获取方式仍需确定</t>
+          <t>NCBI 核酸记录；带版本号的 FASTA 获取地址另列</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>按相同生物名称提出的参考序列；尚未测试分离株、变体和靶标是否兼容。</t>
+          <t>固定使用 Wuhan-Hu-1 参考；尚未检查与所选样本及靶标的匹配程度。</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>查看来源</t>
-        </is>
-      </c>
+          <t>https://eutils.ncbi.nlm.nih.gov/entrez/eutils/efetch.fcgi?db=nuccore&amp;id=NC_045512.2&amp;rettype=fasta&amp;retmode=text</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="n"/>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr"/>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr"/>
     </row>
     <row r="16" ht="126" customHeight="1">
       <c r="A16" s="6" t="n">
@@ -1237,22 +1579,45 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>查看来源</t>
+          <t>https://www.ncbi.nlm.nih.gov/datasets/genome/GCA_900067695.1/</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>直接 gzip FASTA 路径</t>
+          <t>NCBI 组装记录；FASTA 直链另列</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>提出的同物种组装版本；样本、品系、栽培品种和靶标匹配情况及 FASTA 内容均未核实。</t>
+          <t>挪威云杉靶向输入使用同物种参考基因组；尚未检查样本和靶标的匹配程度。</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>查看来源</t>
+          <t>https://ftp.ncbi.nlm.nih.gov/genomes/all/GCA/900/067/695/GCA_900067695.1_Pabies01/GCA_900067695.1_Pabies01_genomic.fna.gz</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>4038780371</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>f23f2f85b0302fbbaed95d159e0b6a6f</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>2016-11-09</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>https://ftp.ncbi.nlm.nih.gov/genomes/all/GCA/900/067/695/GCA_900067695.1_Pabies01/md5checksums.txt</t>
         </is>
       </c>
     </row>
@@ -1277,22 +1642,45 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>查看来源</t>
+          <t>https://www.ncbi.nlm.nih.gov/datasets/genome/GCF_001683475.1/</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>直接 gzip FASTA 路径</t>
+          <t>NCBI 组装记录；FASTA 直链另列</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>提出的同物种组装版本；样本、品系、栽培品种和靶标匹配情况及 FASTA 内容均未核实。</t>
+          <t>QQ74 藜麦参考基因组；尚未检查样本品种是否一致。</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>查看来源</t>
+          <t>https://ftp.ncbi.nlm.nih.gov/genomes/all/GCF/001/683/475/GCF_001683475.1_ASM168347v1/GCF_001683475.1_ASM168347v1_genomic.fna.gz</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>395946550</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>7ba8333bed6ee71c631410104d735017</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>2017-05-19</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>https://ftp.ncbi.nlm.nih.gov/genomes/all/GCF/001/683/475/GCF_001683475.1_ASM168347v1/md5checksums.txt</t>
         </is>
       </c>
     </row>
@@ -1317,104 +1705,167 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>查看来源</t>
+          <t>https://www.ncbi.nlm.nih.gov/datasets/genome/GCF_003668045.3/</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>直接 gzip FASTA 路径</t>
+          <t>NCBI 组装记录；FASTA 直链另列</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>提出的同物种组装版本；样本、品系、栽培品种和靶标匹配情况及 FASTA 内容均未核实。</t>
+          <t>CHO 输入使用 17A/GY 中国仓鼠参考基因组；尚未测量细胞系差异。</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>查看来源</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="78" customHeight="1">
+          <t>https://ftp.ncbi.nlm.nih.gov/genomes/all/GCF/003/668/045/GCF_003668045.3_CriGri-PICRH-1.0/GCF_003668045.3_CriGri-PICRH-1.0_genomic.fna.gz</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>749193397</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>9c7ed3f95a6fe684157ff4480a3ece2d</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>2020-06-11</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>https://ftp.ncbi.nlm.nih.gov/genomes/all/GCF/003/668/045/GCF_003668045.3_CriGri-PICRH-1.0/md5checksums.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="95" customHeight="1">
       <c r="A19" s="6" t="n">
         <v>18</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Triticum_aestivum_Renan_v2.1</t>
+          <t>IWGSC CS RefSeq v2.1</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Triticum aestivum cultivar Renan</t>
+          <t>Triticum aestivum</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>GCA_937894285.1</t>
+          <t>GCF_018294505.1</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>查看来源</t>
+          <t>https://www.ncbi.nlm.nih.gov/datasets/genome/GCF_018294505.1/</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>登录页面；后续需选定确切的 FASTA 文件</t>
+          <t>NCBI 组装记录；FASTA 直链另列</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>同物种、不同栽培品种：为 Thatcher 小麦读段建议使用 Renan 组装；是否精确匹配尚未核实。</t>
+          <t>Thatcher 小麦读段使用中国春参考基因组，两者品种不同。</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>查看来源</t>
+          <t>https://ftp.ncbi.nlm.nih.gov/genomes/all/GCF/018/294/505/GCF_018294505.1_IWGSC_CS_RefSeq_v2.1/GCF_018294505.1_IWGSC_CS_RefSeq_v2.1_genomic.fna.gz</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>4338081367</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>13acbd8dfa42164e3143543918e8e6a3</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>2021-05-06</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>https://ftp.ncbi.nlm.nih.gov/genomes/all/GCF/018/294/505/GCF_018294505.1_IWGSC_CS_RefSeq_v2.1/md5checksums.txt</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H19"/>
+  <autoFilter ref="A1:M19"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M4" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M17" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="rId53"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0"/>
@@ -17946,7 +18397,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>1.1.0；版本说明见 VERSIONING.md。核验状态另按日期记录。</t>
+          <t>1.2.0；版本说明见 VERSIONING.md。核验状态另按日期记录。</t>
         </is>
       </c>
     </row>
@@ -18030,7 +18481,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>已使用的参考序列身份具有稳定的 fa 编号 和精确版本。登录页面不是直接 FASTA 链接。凡未获批准的混合物/特征定义，仍标为未明确。</t>
+          <t>这 18 项参考序列于 2026 年 10 月 27 日对照 NCBI 核对。各物种采用 NCBI 当前指定的参考基因组；大肠杆菌输入保留与样本品系相符的 MG1655 参考。SARS-CoV-2 仍使用固定参考 NC_045512.2。当前参考基因组的发布日期可能较早，它不一定是最近提交的组装。“参考序列”工作表和参考序列表列出确切版本、下载地址及可查到的发布者 MD5。本次没有下载 FASTA 文件。同一物种的参考基因组不一定与样本、品种或转录本靶标完全匹配；混合群落和标签文库没有指定单一基因组参考。</t>
         </is>
       </c>
     </row>
@@ -18423,7 +18874,7 @@
       </c>
       <c r="X3" s="3" t="inlineStr">
         <is>
-          <t>fa 编号 1 / GCF_000001405.39</t>
+          <t>fa 编号 1 / GCF_000001405.40</t>
         </is>
       </c>
       <c r="Y3" s="3" t="n"/>
@@ -18543,7 +18994,7 @@
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t>fa 编号 1 / GCF_000001405.39</t>
+          <t>fa 编号 1 / GCF_000001405.40</t>
         </is>
       </c>
       <c r="Y4" s="3" t="n"/>
@@ -18663,7 +19114,7 @@
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t>fa 编号 1 / GCF_000001405.39</t>
+          <t>fa 编号 1 / GCF_000001405.40</t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
@@ -18787,7 +19238,7 @@
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t>fa 编号 1 / GCF_000001405.39</t>
+          <t>fa 编号 1 / GCF_000001405.40</t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
@@ -18911,7 +19362,7 @@
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t>fa 编号 1 / GCF_000001405.39</t>
+          <t>fa 编号 1 / GCF_000001405.40</t>
         </is>
       </c>
       <c r="Y7" s="3" t="n"/>
@@ -19023,7 +19474,7 @@
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t>fa 编号 1 / GCF_000001405.39</t>
+          <t>fa 编号 1 / GCF_000001405.40</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
@@ -19147,7 +19598,7 @@
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t>fa 编号 1 / GCF_000001405.39</t>
+          <t>fa 编号 1 / GCF_000001405.40</t>
         </is>
       </c>
       <c r="Y9" s="3" t="n"/>
@@ -19271,7 +19722,7 @@
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t>fa 编号 1 / GCF_000001405.39</t>
+          <t>fa 编号 1 / GCF_000001405.40</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
@@ -19395,7 +19846,7 @@
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t>fa 编号 1 / GCF_000001405.39</t>
+          <t>fa 编号 1 / GCF_000001405.40</t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
@@ -19519,7 +19970,7 @@
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t>fa 编号 10 / GCA_902167145.1</t>
+          <t>fa 编号 10 / GCF_902167145.1</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
@@ -19635,7 +20086,7 @@
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t>fa 编号 1 / GCF_000001405.39</t>
+          <t>fa 编号 1 / GCF_000001405.40</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
@@ -19991,7 +20442,7 @@
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>fa 编号 2 / GCA_000003025.6</t>
+          <t>fa 编号 2 / GCF_054392235.1</t>
         </is>
       </c>
       <c r="Y16" s="3" t="n"/>
@@ -20111,7 +20562,7 @@
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>fa 编号 3 / GCF_000001635.24</t>
+          <t>fa 编号 3 / GCF_000001635.27</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
@@ -20235,7 +20686,7 @@
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t>fa 编号 18 / GCA_937894285.1</t>
+          <t>fa 编号 18 / GCF_018294505.1</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
@@ -20359,7 +20810,7 @@
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t>fa 编号 6 / GCA_000226075.1</t>
+          <t>fa 编号 6 / GCF_000226075.1</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
@@ -20603,7 +21054,7 @@
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t>fa 编号 12 / GCA_016699485.1</t>
+          <t>fa 编号 12 / GCF_016699485.2</t>
         </is>
       </c>
       <c r="Y21" s="3" t="n"/>
@@ -20723,7 +21174,7 @@
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t>fa 编号 1 / GCF_000001405.39</t>
+          <t>fa 编号 1 / GCF_000001405.40</t>
         </is>
       </c>
       <c r="Y22" s="3" t="n"/>
@@ -21091,7 +21542,7 @@
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t>fa 编号 1 / GCF_000001405.39</t>
+          <t>fa 编号 1 / GCF_000001405.40</t>
         </is>
       </c>
       <c r="Y25" s="3" t="n"/>
@@ -21335,7 +21786,7 @@
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t>fa 编号 1 / GCF_000001405.39</t>
+          <t>fa 编号 1 / GCF_000001405.40</t>
         </is>
       </c>
       <c r="Y27" s="3" t="n"/>
@@ -21447,7 +21898,7 @@
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t>fa 编号 1 / GCF_000001405.39</t>
+          <t>fa 编号 1 / GCF_000001405.40</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
@@ -21563,7 +22014,7 @@
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t>fa 编号 1 / GCF_000001405.39</t>
+          <t>fa 编号 1 / GCF_000001405.40</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
@@ -21679,7 +22130,7 @@
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t>fa 编号 1 / GCF_000001405.39</t>
+          <t>fa 编号 1 / GCF_000001405.40</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
@@ -21803,7 +22254,7 @@
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t>fa 编号 3 / GCF_000001635.24</t>
+          <t>fa 编号 3 / GCF_000001635.27</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
@@ -22043,7 +22494,7 @@
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t>fa 编号 1 / GCF_000001405.39</t>
+          <t>fa 编号 1 / GCF_000001405.40</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
@@ -22279,7 +22730,7 @@
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t>fa 编号 1 / GCF_000001405.39</t>
+          <t>fa 编号 1 / GCF_000001405.40</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
@@ -22403,7 +22854,7 @@
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t>fa 编号 1 / GCF_000001405.39</t>
+          <t>fa 编号 1 / GCF_000001405.40</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
@@ -22529,7 +22980,7 @@
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>fa 编号 8 / GCA_014636035.1</t>
+          <t>fa 编号 8 / GCF_034140825.1</t>
         </is>
       </c>
       <c r="Y37" s="3" t="n"/>
@@ -22651,7 +23102,7 @@
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t>fa 编号 1 / GCF_000001405.39；fa 编号 13 / GCF_000001215.4</t>
+          <t>fa 编号 1 / GCF_000001405.40；fa 编号 13 / GCF_000001215.4</t>
         </is>
       </c>
       <c r="Y38" s="3" t="n"/>
@@ -22879,7 +23330,7 @@
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t>fa 编号 1 / GCF_000001405.39</t>
+          <t>fa 编号 1 / GCF_000001405.40</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
@@ -22995,7 +23446,7 @@
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t>fa 编号 8 / GCA_014636035.1</t>
+          <t>fa 编号 8 / GCF_034140825.1</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
@@ -31705,7 +32156,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>这次常规小麦重测序运行补充了大型多倍体作物基因组。纳入一个 Thatcher 样本的两个 FASTQ 端。主要研究报告该样本约有 5,425 亿个碱基，覆盖深度为 35×；这是实际研究输入，并非为凑基准规模而截取的子集。建议使用的 Renan 组装来自同一物种的另一栽培品种。</t>
+          <t>这次常规小麦重测序运行补充了大型多倍体作物基因组。纳入一个 Thatcher 样本的两个 FASTQ 端。主要研究报告该样本约有 5,425 亿个碱基，覆盖深度为 35×；这是实际研究输入，并非为凑基准规模而截取的子集。建议使用的 中国春 组装来自同一物种的另一栽培品种。</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -31715,7 +32166,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>建议的参考序列来自 Renan，而非 Thatcher；读段与参考序列是否精确匹配尚未核实。文档记录了名义上的双端 150 碱基测序，但尚未检查实际 FASTQ 的读长、质量值、标题行和完整性。</t>
+          <t>建议的参考序列来自 中国春，而非 Thatcher；读段与参考序列是否精确匹配尚未核实。文档记录了名义上的双端 150 碱基测序，但尚未检查实际 FASTQ 的读长、质量值、标题行和完整性。</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -32175,7 +32626,7 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>获取登记的两个档案配对端，并验证完整性和配对关系。保留所选 FASTQ 的确切表示和顺序。拟议的同物种参考序列为 GRCm38.p4；确切供体亚系、转录本/patch 等价性以及研究所用辅助 ERCC 版本仍未核实。通用无损 FASTQ 压缩不需要这些解释性资源。</t>
+          <t>获取登记的两个档案配对端，并验证完整性和配对关系。保留所选 FASTQ 的确切表示和顺序。拟议的同物种参考序列为 GRCm39；确切供体亚系、转录本/patch 等价性以及研究所用辅助 ERCC 版本仍未核实。通用无损 FASTQ 压缩不需要这些解释性资源。</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -33429,7 +33880,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>建议的参考序列来自 Renan，而非 Thatcher；读段与参考序列是否精确匹配尚未核实。文档记录了名义上的双端 150 碱基测序，但尚未检查实际 FASTQ 的读长、质量值、标题行和完整性。</t>
+          <t>建议的参考序列来自 中国春，而非 Thatcher；读段与参考序列是否精确匹配尚未核实。文档记录了名义上的双端 150 碱基测序，但尚未检查实际 FASTQ 的读长、质量值、标题行和完整性。</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -39349,7 +39800,7 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>官方组装元数据标识 Triticum_aestivum_Renan_v2.1，GCA_937894285.1，assemblydate2022-0…</t>
+          <t>官方组装元数据标识 Triticum_aestivum_中国春_v2.1，GCF_018294505.1，assemblydate2022-0…</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
@@ -39364,7 +39815,7 @@
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>官方组装元数据标识 Triticum_aestivum_Renan_v2.1，GCA_937894285.1，组装日期为2022-08。</t>
+          <t>官方组装元数据标识 Triticum_aestivum_中国春_v2.1，GCF_018294505.1，组装日期为2022-08。</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
@@ -39646,7 +40097,7 @@
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>该论文描述的是 Renan 参考基因组组装。本项目选择的重测序读段来自不同栽培品种 Thatcher。</t>
+          <t>该论文描述的是 中国春 参考基因组组装。本项目选择的重测序读段来自不同栽培品种 Thatcher。</t>
         </is>
       </c>
       <c r="F83" s="3" t="inlineStr">
@@ -40633,12 +41084,12 @@
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>这次常规小麦重测序运行补充了大型多倍体作物基因组。纳入一个 Thatcher 样本的两个 FASTQ 端。主要研究报告该样本约有 5,425 亿个碱基，覆盖深度为 35×；这是实际研究输入，并非为凑基准规模而截取的子集。建议使用的 Renan 组装来自同一物种的另一栽培品种。</t>
+          <t>这次常规小麦重测序运行补充了大型多倍体作物基因组。纳入一个 Thatcher 样本的两个 FASTQ 端。主要研究报告该样本约有 5,425 亿个碱基，覆盖深度为 35×；这是实际研究输入，并非为凑基准规模而截取的子集。建议使用的 中国春 组装来自同一物种的另一栽培品种。</t>
         </is>
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>建议的参考序列来自 Renan，而非 Thatcher；读段与参考序列是否精确匹配尚未核实。文档记录了名义上的双端 150 碱基测序，但尚未检查实际 FASTQ 的读长、质量值、标题行和完整性。</t>
+          <t>建议的参考序列来自 中国春，而非 Thatcher；读段与参考序列是否精确匹配尚未核实。文档记录了名义上的双端 150 碱基测序，但尚未检查实际 FASTQ 的读长、质量值、标题行和完整性。</t>
         </is>
       </c>
       <c r="G104" s="3" t="inlineStr">
